--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_individual_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_individual_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.05529334970248551</v>
       </c>
       <c r="C2" t="n">
-        <v>74553264</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>74553264</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>49255707</v>
+        <v>3542160</v>
       </c>
       <c r="L2" t="n">
-        <v>26817590</v>
+        <v>1660674</v>
       </c>
       <c r="M2" t="n">
-        <v>6572359</v>
+        <v>338353</v>
       </c>
       <c r="N2" t="n">
-        <v>346442</v>
+        <v>12188</v>
       </c>
       <c r="O2" t="n">
-        <v>3989397</v>
+        <v>216243</v>
       </c>
       <c r="P2" t="n">
-        <v>1664046</v>
+        <v>95455</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998725652694702</v>
+        <v>0.9997677803039551</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8336921334266663</v>
+        <v>0.7193809747695923</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6927187442779541</v>
+        <v>0.5147995948791504</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5865252614021301</v>
+        <v>0.3624415993690491</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4024810492992401</v>
+        <v>0.1704686880111694</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6539778709411621</v>
+        <v>0.4255529046058655</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7170951962471008</v>
+        <v>0.4939737915992737</v>
       </c>
       <c r="X2" t="n">
-        <v>74553264</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>74553264</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>47982023</v>
+        <v>3493153</v>
       </c>
       <c r="AG2" t="n">
-        <v>25073837</v>
+        <v>1600240</v>
       </c>
       <c r="AH2" t="n">
-        <v>5967639</v>
+        <v>317977</v>
       </c>
       <c r="AI2" t="n">
-        <v>310462</v>
+        <v>11503</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3684743</v>
+        <v>204180</v>
       </c>
       <c r="AK2" t="n">
-        <v>1561091</v>
+        <v>89730</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8097841143608093</v>
+        <v>0.7074398994445801</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6521316170692444</v>
+        <v>0.4994371235370636</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5369819402694702</v>
+        <v>0.3433476388454437</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.2927406430244446</v>
+        <v>0.1301568299531937</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6043883562088013</v>
+        <v>0.4018864035606384</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.6731289029121399</v>
+        <v>0.4642896056175232</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.01737264878728136</v>
       </c>
       <c r="C3" t="n">
-        <v>3626</v>
+        <v>656</v>
       </c>
       <c r="D3" t="n">
-        <v>49255707</v>
+        <v>3542160</v>
       </c>
       <c r="E3" t="n">
-        <v>8458541</v>
+        <v>1120732</v>
       </c>
       <c r="F3" t="n">
-        <v>622437</v>
+        <v>110617</v>
       </c>
       <c r="G3" t="n">
-        <v>77687</v>
+        <v>10795</v>
       </c>
       <c r="H3" t="n">
-        <v>53418</v>
+        <v>14983</v>
       </c>
       <c r="I3" t="n">
-        <v>9564</v>
+        <v>2958</v>
       </c>
       <c r="J3" t="n">
-        <v>118282034</v>
+        <v>9856185</v>
       </c>
       <c r="K3" t="n">
-        <v>124538117</v>
+        <v>9885759</v>
       </c>
       <c r="L3" t="n">
-        <v>141862582</v>
+        <v>11189032</v>
       </c>
       <c r="M3" t="n">
-        <v>177000115</v>
+        <v>14532659</v>
       </c>
       <c r="N3" t="n">
-        <v>191262739</v>
+        <v>15921520</v>
       </c>
       <c r="O3" t="n">
-        <v>184611504</v>
+        <v>15266124</v>
       </c>
       <c r="P3" t="n">
-        <v>189865714</v>
+        <v>15778566</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.842251718044281</v>
+        <v>0.737504243850708</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6861127018928528</v>
+        <v>0.5007796883583069</v>
       </c>
       <c r="T3" t="n">
-        <v>0.586217999458313</v>
+        <v>0.358973890542984</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3244637846946716</v>
+        <v>0.1360708326101303</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6515970230102539</v>
+        <v>0.4220421314239502</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7164598107337952</v>
+        <v>0.4919092953205109</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>47982023</v>
+        <v>3493153</v>
       </c>
       <c r="Z3" t="n">
-        <v>9522879</v>
+        <v>1148330</v>
       </c>
       <c r="AA3" t="n">
-        <v>700350</v>
+        <v>117926</v>
       </c>
       <c r="AB3" t="n">
-        <v>191118</v>
+        <v>21139</v>
       </c>
       <c r="AC3" t="n">
-        <v>71585</v>
+        <v>18489</v>
       </c>
       <c r="AD3" t="n">
-        <v>13025</v>
+        <v>3864</v>
       </c>
       <c r="AE3" t="n">
-        <v>118291536</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>123092987</v>
+        <v>9822914</v>
       </c>
       <c r="AG3" t="n">
-        <v>140383319</v>
+        <v>11150376</v>
       </c>
       <c r="AH3" t="n">
-        <v>176487684</v>
+        <v>14519713</v>
       </c>
       <c r="AI3" t="n">
-        <v>191026989</v>
+        <v>15903954</v>
       </c>
       <c r="AJ3" t="n">
-        <v>184310404</v>
+        <v>15254153</v>
       </c>
       <c r="AK3" t="n">
-        <v>189764140</v>
+        <v>15772817</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8204723000526428</v>
+        <v>0.7273006439208984</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6414998173713684</v>
+        <v>0.4825556576251984</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5322803258895874</v>
+        <v>0.3373560905456543</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.2907663583755493</v>
+        <v>0.1284232586622238</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6018372178077698</v>
+        <v>0.3984987437725067</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.6721322536468506</v>
+        <v>0.4624066054821014</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.1069592155238431</v>
       </c>
       <c r="C4" t="n">
-        <v>1513</v>
+        <v>250</v>
       </c>
       <c r="D4" t="n">
-        <v>9048224</v>
+        <v>1228792</v>
       </c>
       <c r="E4" t="n">
-        <v>26817590</v>
+        <v>1660674</v>
       </c>
       <c r="F4" t="n">
-        <v>2611002</v>
+        <v>316368</v>
       </c>
       <c r="G4" t="n">
-        <v>118938</v>
+        <v>17048</v>
       </c>
       <c r="H4" t="n">
-        <v>422452</v>
+        <v>78263</v>
       </c>
       <c r="I4" t="n">
-        <v>66555</v>
+        <v>14782</v>
       </c>
       <c r="J4" t="n">
-        <v>9502</v>
+        <v>1443</v>
       </c>
       <c r="K4" t="n">
-        <v>9825703</v>
+        <v>1381740</v>
       </c>
       <c r="L4" t="n">
-        <v>11895944</v>
+        <v>1565191</v>
       </c>
       <c r="M4" t="n">
-        <v>4633226</v>
+        <v>595185</v>
       </c>
       <c r="N4" t="n">
-        <v>514324</v>
+        <v>59309</v>
       </c>
       <c r="O4" t="n">
-        <v>2110805</v>
+        <v>291903</v>
       </c>
       <c r="P4" t="n">
-        <v>656491</v>
+        <v>97784</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999362826347351</v>
+        <v>0.9998838901519775</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8379501104354858</v>
+        <v>0.7283298969268799</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6893998980522156</v>
+        <v>0.5076928734779358</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5863715410232544</v>
+        <v>0.3606994152069092</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3592859506607056</v>
+        <v>0.1513397991657257</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6527852416038513</v>
+        <v>0.4237902462482452</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7167773246765137</v>
+        <v>0.4929393529891968</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>10316149</v>
+        <v>1270840</v>
       </c>
       <c r="Z4" t="n">
-        <v>25073837</v>
+        <v>1600240</v>
       </c>
       <c r="AA4" t="n">
-        <v>2907345</v>
+        <v>320069</v>
       </c>
       <c r="AB4" t="n">
-        <v>198806</v>
+        <v>23306</v>
       </c>
       <c r="AC4" t="n">
-        <v>507223</v>
+        <v>85088</v>
       </c>
       <c r="AD4" t="n">
-        <v>82914</v>
+        <v>16634</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>11270833</v>
+        <v>1444585</v>
       </c>
       <c r="AG4" t="n">
-        <v>13375207</v>
+        <v>1603847</v>
       </c>
       <c r="AH4" t="n">
-        <v>5145657</v>
+        <v>608131</v>
       </c>
       <c r="AI4" t="n">
-        <v>750074</v>
+        <v>76875</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2411905</v>
+        <v>303874</v>
       </c>
       <c r="AK4" t="n">
-        <v>758065</v>
+        <v>103533</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8150931596755981</v>
+        <v>0.7172327637672424</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.646772027015686</v>
+        <v>0.4908512830734253</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5346208214759827</v>
+        <v>0.3403254747390747</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.2917501628398895</v>
+        <v>0.1292842328548431</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6031100153923035</v>
+        <v>0.4001854360103607</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.672630250453949</v>
+        <v>0.4633462131023407</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1582</v>
+        <v>240</v>
       </c>
       <c r="D5" t="n">
-        <v>555909</v>
+        <v>112786</v>
       </c>
       <c r="E5" t="n">
-        <v>2724695</v>
+        <v>320150</v>
       </c>
       <c r="F5" t="n">
-        <v>6572359</v>
+        <v>338353</v>
       </c>
       <c r="G5" t="n">
-        <v>174335</v>
+        <v>17251</v>
       </c>
       <c r="H5" t="n">
-        <v>1028061</v>
+        <v>126519</v>
       </c>
       <c r="I5" t="n">
-        <v>154518</v>
+        <v>27257</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9225273</v>
+        <v>1260741</v>
       </c>
       <c r="L5" t="n">
-        <v>12268684</v>
+        <v>1655503</v>
       </c>
       <c r="M5" t="n">
-        <v>4639100</v>
+        <v>604203</v>
       </c>
       <c r="N5" t="n">
-        <v>721295</v>
+        <v>77383</v>
       </c>
       <c r="O5" t="n">
-        <v>2133094</v>
+        <v>296130</v>
       </c>
       <c r="P5" t="n">
-        <v>658549</v>
+        <v>98595</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999507069587708</v>
+        <v>0.9999102354049683</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9012108445167542</v>
+        <v>0.8355684280395508</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8746939301490784</v>
+        <v>0.7995884418487549</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9519181847572327</v>
+        <v>0.9253666400909424</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9935926795005798</v>
+        <v>0.9914941787719727</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9779931902885437</v>
+        <v>0.9634089469909668</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9931808114051819</v>
+        <v>0.9877800941467285</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>685286</v>
+        <v>127400</v>
       </c>
       <c r="Z5" t="n">
-        <v>3017666</v>
+        <v>321330</v>
       </c>
       <c r="AA5" t="n">
-        <v>5967639</v>
+        <v>317977</v>
       </c>
       <c r="AB5" t="n">
-        <v>201987</v>
+        <v>18196</v>
       </c>
       <c r="AC5" t="n">
-        <v>1155657</v>
+        <v>128388</v>
       </c>
       <c r="AD5" t="n">
-        <v>183224</v>
+        <v>29265</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>10498957</v>
+        <v>1309748</v>
       </c>
       <c r="AG5" t="n">
-        <v>14012437</v>
+        <v>1715937</v>
       </c>
       <c r="AH5" t="n">
-        <v>5243820</v>
+        <v>624579</v>
       </c>
       <c r="AI5" t="n">
-        <v>757275</v>
+        <v>78068</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2437748</v>
+        <v>308193</v>
       </c>
       <c r="AK5" t="n">
-        <v>761504</v>
+        <v>104320</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8871123790740967</v>
+        <v>0.8286083340644836</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8579809069633484</v>
+        <v>0.7934224605560303</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9461252093315125</v>
+        <v>0.9232931137084961</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9921836256980896</v>
+        <v>0.9903584718704224</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9748520255088806</v>
+        <v>0.9619134068489075</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9921202659606934</v>
+        <v>0.9870660901069641</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1898</v>
+        <v>200</v>
       </c>
       <c r="D6" t="n">
-        <v>154587</v>
+        <v>19397</v>
       </c>
       <c r="E6" t="n">
-        <v>195070</v>
+        <v>23995</v>
       </c>
       <c r="F6" t="n">
-        <v>218752</v>
+        <v>17653</v>
       </c>
       <c r="G6" t="n">
-        <v>346442</v>
+        <v>12188</v>
       </c>
       <c r="H6" t="n">
-        <v>126738</v>
+        <v>12831</v>
       </c>
       <c r="I6" t="n">
-        <v>24250</v>
+        <v>3307</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>175542</v>
+        <v>20393</v>
       </c>
       <c r="Z6" t="n">
-        <v>209618</v>
+        <v>24197</v>
       </c>
       <c r="AA6" t="n">
-        <v>205739</v>
+        <v>17122</v>
       </c>
       <c r="AB6" t="n">
-        <v>310462</v>
+        <v>11503</v>
       </c>
       <c r="AC6" t="n">
-        <v>139172</v>
+        <v>12946</v>
       </c>
       <c r="AD6" t="n">
-        <v>27204</v>
+        <v>3410</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>598</v>
+        <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>62475</v>
+        <v>18775</v>
       </c>
       <c r="E7" t="n">
-        <v>466978</v>
+        <v>88357</v>
       </c>
       <c r="F7" t="n">
-        <v>1077817</v>
+        <v>128490</v>
       </c>
       <c r="G7" t="n">
-        <v>123622</v>
+        <v>10964</v>
       </c>
       <c r="H7" t="n">
-        <v>3989397</v>
+        <v>216243</v>
       </c>
       <c r="I7" t="n">
-        <v>401604</v>
+        <v>49480</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>86211</v>
+        <v>22972</v>
       </c>
       <c r="Z7" t="n">
-        <v>561132</v>
+        <v>96320</v>
       </c>
       <c r="AA7" t="n">
-        <v>1203889</v>
+        <v>127732</v>
       </c>
       <c r="AB7" t="n">
-        <v>134818</v>
+        <v>10809</v>
       </c>
       <c r="AC7" t="n">
-        <v>3684743</v>
+        <v>204180</v>
       </c>
       <c r="AD7" t="n">
-        <v>451698</v>
+        <v>50360</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>285</v>
+        <v>33</v>
       </c>
       <c r="D8" t="n">
-        <v>4508</v>
+        <v>1990</v>
       </c>
       <c r="E8" t="n">
-        <v>50660</v>
+        <v>11957</v>
       </c>
       <c r="F8" t="n">
-        <v>103218</v>
+        <v>22057</v>
       </c>
       <c r="G8" t="n">
-        <v>19742</v>
+        <v>3251</v>
       </c>
       <c r="H8" t="n">
-        <v>480136</v>
+        <v>59307</v>
       </c>
       <c r="I8" t="n">
-        <v>1664046</v>
+        <v>95455</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>7645</v>
+        <v>2980</v>
       </c>
       <c r="Z8" t="n">
-        <v>63912</v>
+        <v>13670</v>
       </c>
       <c r="AA8" t="n">
-        <v>128334</v>
+        <v>25282</v>
       </c>
       <c r="AB8" t="n">
-        <v>23345</v>
+        <v>3425</v>
       </c>
       <c r="AC8" t="n">
-        <v>538268</v>
+        <v>58963</v>
       </c>
       <c r="AD8" t="n">
-        <v>1561091</v>
+        <v>89730</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
